--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.19822356456883</v>
+        <v>8.969711329242434</v>
       </c>
       <c r="D2" t="n">
-        <v>56.78537080518562</v>
+        <v>9.227622755842663</v>
       </c>
       <c r="E2" t="n">
-        <v>9.877892075444091</v>
+        <v>1.605157462259665</v>
       </c>
       <c r="F2" t="n">
-        <v>9.600323916149186</v>
+        <v>1.560052636374243</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>74.95400771545701</v>
+        <v>12.18002625376177</v>
       </c>
       <c r="D3" t="n">
-        <v>75.98601863748399</v>
+        <v>12.34772802859115</v>
       </c>
       <c r="E3" t="n">
-        <v>9.877892075444091</v>
+        <v>1.605157462259665</v>
       </c>
       <c r="F3" t="n">
-        <v>9.600323916149186</v>
+        <v>1.560052636374243</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
